--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T01:52:46+00:00</t>
+    <t>2024-12-30T05:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T05:25:46+00:00</t>
+    <t>2024-12-30T06:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T06:06:44+00:00</t>
+    <t>2024-12-30T09:02:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T09:02:09+00:00</t>
+    <t>2024-12-30T09:11:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T09:11:40+00:00</t>
+    <t>2024-12-30T09:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T09:24:38+00:00</t>
+    <t>2024-12-30T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T10:20:10+00:00</t>
+    <t>2024-12-31T04:42:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-31T04:42:12+00:00</t>
+    <t>2025-01-02T04:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T04:55:17+00:00</t>
+    <t>2025-01-02T05:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T06:27:10+00:00</t>
+    <t>2025-01-02T07:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T01:45:27+00:00</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>次回摂取予定日</t>
+    <t>次回接種予定日</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -257,9 +257,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>次回接種予定日</t>
   </si>
   <si>
     <t>次回接種を予定している日、期限</t>
@@ -848,10 +845,10 @@
         <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -911,10 +908,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -922,10 +919,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -936,25 +933,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1005,13 +1002,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1020,15 +1017,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1051,13 +1048,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1096,19 +1093,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1120,7 +1117,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1128,10 +1125,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1139,10 +1136,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1154,16 +1151,16 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1213,13 +1210,13 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1228,15 +1225,15 @@
         <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1247,7 +1244,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1259,13 +1256,13 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1316,22 +1313,22 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
